--- a/public/templates/importacao-condominios.xlsx
+++ b/public/templates/importacao-condominios.xlsx
@@ -204,23 +204,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelaDados" displayName="TabelaDados" ref="A1:I50">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="carteira"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="nome"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="cnpj"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="administradora"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="vencimento_cota_dia"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="valor_cota_condominial"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="inicio_cobranca_dias"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="status"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="observacoes"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -2799,9 +2782,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/public/templates/importacao-condominios.xlsx
+++ b/public/templates/importacao-condominios.xlsx
@@ -401,9 +401,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A10"/>
-  <cols>
-    <col min="1" max="1" width="120.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -464,22 +461,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M201"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="21.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="27.83203125" customWidth="1"/>
-    <col min="10" max="10" width="39.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:U201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -495,30 +477,54 @@
         <v>cnpj</v>
       </c>
       <c r="E1" t="str">
+        <v>endereco_logradouro</v>
+      </c>
+      <c r="F1" t="str">
+        <v>endereco_numero</v>
+      </c>
+      <c r="G1" t="str">
+        <v>endereco_complemento</v>
+      </c>
+      <c r="H1" t="str">
+        <v>endereco_bairro</v>
+      </c>
+      <c r="I1" t="str">
+        <v>endereco_cidade</v>
+      </c>
+      <c r="J1" t="str">
+        <v>endereco_uf</v>
+      </c>
+      <c r="K1" t="str">
+        <v>endereco_cep</v>
+      </c>
+      <c r="L1" t="str">
         <v>administradora</v>
       </c>
-      <c r="F1" t="str">
+      <c r="M1" t="str">
         <v>vencimento_cota_dia</v>
       </c>
-      <c r="G1" t="str">
+      <c r="N1" t="str">
         <v>valor_cota_condominial</v>
       </c>
-      <c r="H1" t="str">
+      <c r="O1" t="str">
         <v>inicio_cobranca_dias</v>
       </c>
-      <c r="I1" t="str">
+      <c r="P1" t="str">
+        <v>dias_expiracao_regua_pre_juridico</v>
+      </c>
+      <c r="Q1" t="str">
         <v>classificacao_operacional</v>
       </c>
-      <c r="J1" t="str">
+      <c r="R1" t="str">
         <v>parcelas_acordo_sem_aprovacao_sindico</v>
       </c>
-      <c r="K1" t="str">
+      <c r="S1" t="str">
         <v>dias_reemissao_parcela_acordo_atrasada</v>
       </c>
-      <c r="L1" t="str">
+      <c r="T1" t="str">
         <v>status</v>
       </c>
-      <c r="M1" t="str">
+      <c r="U1" t="str">
         <v>observacoes</v>
       </c>
     </row>
@@ -562,6 +568,30 @@
       <c r="M2" t="str">
         <v/>
       </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -603,6 +633,30 @@
       <c r="M3" t="str">
         <v/>
       </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -644,6 +698,30 @@
       <c r="M4" t="str">
         <v/>
       </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -685,6 +763,30 @@
       <c r="M5" t="str">
         <v/>
       </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -726,6 +828,30 @@
       <c r="M6" t="str">
         <v/>
       </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -767,6 +893,30 @@
       <c r="M7" t="str">
         <v/>
       </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -808,6 +958,30 @@
       <c r="M8" t="str">
         <v/>
       </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -849,6 +1023,30 @@
       <c r="M9" t="str">
         <v/>
       </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v/>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -890,6 +1088,30 @@
       <c r="M10" t="str">
         <v/>
       </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -931,6 +1153,30 @@
       <c r="M11" t="str">
         <v/>
       </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
+        <v/>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -972,6 +1218,30 @@
       <c r="M12" t="str">
         <v/>
       </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
+        <v/>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1013,6 +1283,30 @@
       <c r="M13" t="str">
         <v/>
       </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
+        <v/>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -1054,6 +1348,30 @@
       <c r="M14" t="str">
         <v/>
       </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
+        <v/>
+      </c>
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1095,6 +1413,30 @@
       <c r="M15" t="str">
         <v/>
       </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
+        <v/>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1136,6 +1478,30 @@
       <c r="M16" t="str">
         <v/>
       </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v/>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1177,6 +1543,30 @@
       <c r="M17" t="str">
         <v/>
       </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v/>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1218,6 +1608,30 @@
       <c r="M18" t="str">
         <v/>
       </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v/>
+      </c>
+      <c r="T18" t="str">
+        <v/>
+      </c>
+      <c r="U18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1259,6 +1673,30 @@
       <c r="M19" t="str">
         <v/>
       </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
+        <v/>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1300,6 +1738,30 @@
       <c r="M20" t="str">
         <v/>
       </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v/>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1341,6 +1803,30 @@
       <c r="M21" t="str">
         <v/>
       </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
+        <v/>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1382,6 +1868,30 @@
       <c r="M22" t="str">
         <v/>
       </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22" t="str">
+        <v/>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1423,6 +1933,30 @@
       <c r="M23" t="str">
         <v/>
       </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23" t="str">
+        <v/>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1464,6 +1998,30 @@
       <c r="M24" t="str">
         <v/>
       </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24" t="str">
+        <v/>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1505,6 +2063,30 @@
       <c r="M25" t="str">
         <v/>
       </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25" t="str">
+        <v/>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -1546,6 +2128,30 @@
       <c r="M26" t="str">
         <v/>
       </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26" t="str">
+        <v/>
+      </c>
+      <c r="T26" t="str">
+        <v/>
+      </c>
+      <c r="U26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1587,6 +2193,30 @@
       <c r="M27" t="str">
         <v/>
       </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27" t="str">
+        <v/>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -1628,6 +2258,30 @@
       <c r="M28" t="str">
         <v/>
       </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28" t="str">
+        <v/>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -1669,6 +2323,30 @@
       <c r="M29" t="str">
         <v/>
       </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v/>
+      </c>
+      <c r="S29" t="str">
+        <v/>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -1710,6 +2388,30 @@
       <c r="M30" t="str">
         <v/>
       </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v/>
+      </c>
+      <c r="S30" t="str">
+        <v/>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -1751,6 +2453,30 @@
       <c r="M31" t="str">
         <v/>
       </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v/>
+      </c>
+      <c r="S31" t="str">
+        <v/>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -1792,6 +2518,30 @@
       <c r="M32" t="str">
         <v/>
       </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v/>
+      </c>
+      <c r="S32" t="str">
+        <v/>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -1833,6 +2583,30 @@
       <c r="M33" t="str">
         <v/>
       </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v/>
+      </c>
+      <c r="S33" t="str">
+        <v/>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
+      <c r="U33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -1874,6 +2648,30 @@
       <c r="M34" t="str">
         <v/>
       </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v/>
+      </c>
+      <c r="S34" t="str">
+        <v/>
+      </c>
+      <c r="T34" t="str">
+        <v/>
+      </c>
+      <c r="U34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -1915,6 +2713,30 @@
       <c r="M35" t="str">
         <v/>
       </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v/>
+      </c>
+      <c r="S35" t="str">
+        <v/>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
+      <c r="U35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -1956,6 +2778,30 @@
       <c r="M36" t="str">
         <v/>
       </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v/>
+      </c>
+      <c r="S36" t="str">
+        <v/>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
+      <c r="U36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -1997,6 +2843,30 @@
       <c r="M37" t="str">
         <v/>
       </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v/>
+      </c>
+      <c r="S37" t="str">
+        <v/>
+      </c>
+      <c r="T37" t="str">
+        <v/>
+      </c>
+      <c r="U37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -2038,6 +2908,30 @@
       <c r="M38" t="str">
         <v/>
       </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v/>
+      </c>
+      <c r="S38" t="str">
+        <v/>
+      </c>
+      <c r="T38" t="str">
+        <v/>
+      </c>
+      <c r="U38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -2079,6 +2973,30 @@
       <c r="M39" t="str">
         <v/>
       </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v/>
+      </c>
+      <c r="S39" t="str">
+        <v/>
+      </c>
+      <c r="T39" t="str">
+        <v/>
+      </c>
+      <c r="U39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -2120,6 +3038,30 @@
       <c r="M40" t="str">
         <v/>
       </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v/>
+      </c>
+      <c r="S40" t="str">
+        <v/>
+      </c>
+      <c r="T40" t="str">
+        <v/>
+      </c>
+      <c r="U40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -2161,6 +3103,30 @@
       <c r="M41" t="str">
         <v/>
       </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v/>
+      </c>
+      <c r="S41" t="str">
+        <v/>
+      </c>
+      <c r="T41" t="str">
+        <v/>
+      </c>
+      <c r="U41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -2202,6 +3168,30 @@
       <c r="M42" t="str">
         <v/>
       </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v/>
+      </c>
+      <c r="S42" t="str">
+        <v/>
+      </c>
+      <c r="T42" t="str">
+        <v/>
+      </c>
+      <c r="U42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -2243,6 +3233,30 @@
       <c r="M43" t="str">
         <v/>
       </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v/>
+      </c>
+      <c r="S43" t="str">
+        <v/>
+      </c>
+      <c r="T43" t="str">
+        <v/>
+      </c>
+      <c r="U43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -2284,6 +3298,30 @@
       <c r="M44" t="str">
         <v/>
       </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v/>
+      </c>
+      <c r="S44" t="str">
+        <v/>
+      </c>
+      <c r="T44" t="str">
+        <v/>
+      </c>
+      <c r="U44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -2325,6 +3363,30 @@
       <c r="M45" t="str">
         <v/>
       </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
+        <v/>
+      </c>
+      <c r="R45" t="str">
+        <v/>
+      </c>
+      <c r="S45" t="str">
+        <v/>
+      </c>
+      <c r="T45" t="str">
+        <v/>
+      </c>
+      <c r="U45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -2366,6 +3428,30 @@
       <c r="M46" t="str">
         <v/>
       </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
+        <v/>
+      </c>
+      <c r="R46" t="str">
+        <v/>
+      </c>
+      <c r="S46" t="str">
+        <v/>
+      </c>
+      <c r="T46" t="str">
+        <v/>
+      </c>
+      <c r="U46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -2407,6 +3493,30 @@
       <c r="M47" t="str">
         <v/>
       </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
+        <v/>
+      </c>
+      <c r="R47" t="str">
+        <v/>
+      </c>
+      <c r="S47" t="str">
+        <v/>
+      </c>
+      <c r="T47" t="str">
+        <v/>
+      </c>
+      <c r="U47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -2448,6 +3558,30 @@
       <c r="M48" t="str">
         <v/>
       </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
+        <v/>
+      </c>
+      <c r="R48" t="str">
+        <v/>
+      </c>
+      <c r="S48" t="str">
+        <v/>
+      </c>
+      <c r="T48" t="str">
+        <v/>
+      </c>
+      <c r="U48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -2489,6 +3623,30 @@
       <c r="M49" t="str">
         <v/>
       </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
+        <v/>
+      </c>
+      <c r="R49" t="str">
+        <v/>
+      </c>
+      <c r="S49" t="str">
+        <v/>
+      </c>
+      <c r="T49" t="str">
+        <v/>
+      </c>
+      <c r="U49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2530,6 +3688,30 @@
       <c r="M50" t="str">
         <v/>
       </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
+        <v/>
+      </c>
+      <c r="T50" t="str">
+        <v/>
+      </c>
+      <c r="U50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -2571,6 +3753,30 @@
       <c r="M51" t="str">
         <v/>
       </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
+        <v/>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
+        <v/>
+      </c>
+      <c r="T51" t="str">
+        <v/>
+      </c>
+      <c r="U51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -2612,6 +3818,30 @@
       <c r="M52" t="str">
         <v/>
       </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
+        <v/>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v/>
+      </c>
+      <c r="T52" t="str">
+        <v/>
+      </c>
+      <c r="U52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -2653,6 +3883,30 @@
       <c r="M53" t="str">
         <v/>
       </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
+        <v/>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v/>
+      </c>
+      <c r="T53" t="str">
+        <v/>
+      </c>
+      <c r="U53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -2694,6 +3948,30 @@
       <c r="M54" t="str">
         <v/>
       </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
+        <v/>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v/>
+      </c>
+      <c r="T54" t="str">
+        <v/>
+      </c>
+      <c r="U54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -2735,6 +4013,30 @@
       <c r="M55" t="str">
         <v/>
       </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
+        <v/>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v/>
+      </c>
+      <c r="T55" t="str">
+        <v/>
+      </c>
+      <c r="U55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -2776,6 +4078,30 @@
       <c r="M56" t="str">
         <v/>
       </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
+        <v/>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v/>
+      </c>
+      <c r="T56" t="str">
+        <v/>
+      </c>
+      <c r="U56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -2817,6 +4143,30 @@
       <c r="M57" t="str">
         <v/>
       </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
+        <v/>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v/>
+      </c>
+      <c r="T57" t="str">
+        <v/>
+      </c>
+      <c r="U57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -2858,6 +4208,30 @@
       <c r="M58" t="str">
         <v/>
       </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
+        <v/>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v/>
+      </c>
+      <c r="T58" t="str">
+        <v/>
+      </c>
+      <c r="U58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -2899,6 +4273,30 @@
       <c r="M59" t="str">
         <v/>
       </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
+        <v/>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v/>
+      </c>
+      <c r="T59" t="str">
+        <v/>
+      </c>
+      <c r="U59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -2940,6 +4338,30 @@
       <c r="M60" t="str">
         <v/>
       </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
+        <v/>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v/>
+      </c>
+      <c r="T60" t="str">
+        <v/>
+      </c>
+      <c r="U60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -2981,6 +4403,30 @@
       <c r="M61" t="str">
         <v/>
       </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
+        <v/>
+      </c>
+      <c r="R61" t="str">
+        <v/>
+      </c>
+      <c r="S61" t="str">
+        <v/>
+      </c>
+      <c r="T61" t="str">
+        <v/>
+      </c>
+      <c r="U61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -3022,6 +4468,30 @@
       <c r="M62" t="str">
         <v/>
       </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
+        <v/>
+      </c>
+      <c r="R62" t="str">
+        <v/>
+      </c>
+      <c r="S62" t="str">
+        <v/>
+      </c>
+      <c r="T62" t="str">
+        <v/>
+      </c>
+      <c r="U62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -3063,6 +4533,30 @@
       <c r="M63" t="str">
         <v/>
       </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
+        <v/>
+      </c>
+      <c r="R63" t="str">
+        <v/>
+      </c>
+      <c r="S63" t="str">
+        <v/>
+      </c>
+      <c r="T63" t="str">
+        <v/>
+      </c>
+      <c r="U63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -3104,6 +4598,30 @@
       <c r="M64" t="str">
         <v/>
       </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
+        <v/>
+      </c>
+      <c r="R64" t="str">
+        <v/>
+      </c>
+      <c r="S64" t="str">
+        <v/>
+      </c>
+      <c r="T64" t="str">
+        <v/>
+      </c>
+      <c r="U64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3145,6 +4663,30 @@
       <c r="M65" t="str">
         <v/>
       </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
+        <v/>
+      </c>
+      <c r="R65" t="str">
+        <v/>
+      </c>
+      <c r="S65" t="str">
+        <v/>
+      </c>
+      <c r="T65" t="str">
+        <v/>
+      </c>
+      <c r="U65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -3186,6 +4728,30 @@
       <c r="M66" t="str">
         <v/>
       </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
+        <v/>
+      </c>
+      <c r="R66" t="str">
+        <v/>
+      </c>
+      <c r="S66" t="str">
+        <v/>
+      </c>
+      <c r="T66" t="str">
+        <v/>
+      </c>
+      <c r="U66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -3227,6 +4793,30 @@
       <c r="M67" t="str">
         <v/>
       </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
+        <v/>
+      </c>
+      <c r="R67" t="str">
+        <v/>
+      </c>
+      <c r="S67" t="str">
+        <v/>
+      </c>
+      <c r="T67" t="str">
+        <v/>
+      </c>
+      <c r="U67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3268,6 +4858,30 @@
       <c r="M68" t="str">
         <v/>
       </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
+        <v/>
+      </c>
+      <c r="R68" t="str">
+        <v/>
+      </c>
+      <c r="S68" t="str">
+        <v/>
+      </c>
+      <c r="T68" t="str">
+        <v/>
+      </c>
+      <c r="U68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -3309,6 +4923,30 @@
       <c r="M69" t="str">
         <v/>
       </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
+        <v/>
+      </c>
+      <c r="R69" t="str">
+        <v/>
+      </c>
+      <c r="S69" t="str">
+        <v/>
+      </c>
+      <c r="T69" t="str">
+        <v/>
+      </c>
+      <c r="U69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -3350,6 +4988,30 @@
       <c r="M70" t="str">
         <v/>
       </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
+        <v/>
+      </c>
+      <c r="R70" t="str">
+        <v/>
+      </c>
+      <c r="S70" t="str">
+        <v/>
+      </c>
+      <c r="T70" t="str">
+        <v/>
+      </c>
+      <c r="U70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -3391,6 +5053,30 @@
       <c r="M71" t="str">
         <v/>
       </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
+        <v/>
+      </c>
+      <c r="R71" t="str">
+        <v/>
+      </c>
+      <c r="S71" t="str">
+        <v/>
+      </c>
+      <c r="T71" t="str">
+        <v/>
+      </c>
+      <c r="U71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -3432,6 +5118,30 @@
       <c r="M72" t="str">
         <v/>
       </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
+        <v/>
+      </c>
+      <c r="R72" t="str">
+        <v/>
+      </c>
+      <c r="S72" t="str">
+        <v/>
+      </c>
+      <c r="T72" t="str">
+        <v/>
+      </c>
+      <c r="U72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -3473,6 +5183,30 @@
       <c r="M73" t="str">
         <v/>
       </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
+        <v/>
+      </c>
+      <c r="R73" t="str">
+        <v/>
+      </c>
+      <c r="S73" t="str">
+        <v/>
+      </c>
+      <c r="T73" t="str">
+        <v/>
+      </c>
+      <c r="U73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -3514,6 +5248,30 @@
       <c r="M74" t="str">
         <v/>
       </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v/>
+      </c>
+      <c r="R74" t="str">
+        <v/>
+      </c>
+      <c r="S74" t="str">
+        <v/>
+      </c>
+      <c r="T74" t="str">
+        <v/>
+      </c>
+      <c r="U74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -3555,6 +5313,30 @@
       <c r="M75" t="str">
         <v/>
       </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
+        <v/>
+      </c>
+      <c r="R75" t="str">
+        <v/>
+      </c>
+      <c r="S75" t="str">
+        <v/>
+      </c>
+      <c r="T75" t="str">
+        <v/>
+      </c>
+      <c r="U75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -3596,6 +5378,30 @@
       <c r="M76" t="str">
         <v/>
       </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
+        <v/>
+      </c>
+      <c r="R76" t="str">
+        <v/>
+      </c>
+      <c r="S76" t="str">
+        <v/>
+      </c>
+      <c r="T76" t="str">
+        <v/>
+      </c>
+      <c r="U76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -3637,6 +5443,30 @@
       <c r="M77" t="str">
         <v/>
       </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
+        <v/>
+      </c>
+      <c r="R77" t="str">
+        <v/>
+      </c>
+      <c r="S77" t="str">
+        <v/>
+      </c>
+      <c r="T77" t="str">
+        <v/>
+      </c>
+      <c r="U77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -3678,6 +5508,30 @@
       <c r="M78" t="str">
         <v/>
       </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
+        <v/>
+      </c>
+      <c r="R78" t="str">
+        <v/>
+      </c>
+      <c r="S78" t="str">
+        <v/>
+      </c>
+      <c r="T78" t="str">
+        <v/>
+      </c>
+      <c r="U78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3719,6 +5573,30 @@
       <c r="M79" t="str">
         <v/>
       </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
+        <v/>
+      </c>
+      <c r="R79" t="str">
+        <v/>
+      </c>
+      <c r="S79" t="str">
+        <v/>
+      </c>
+      <c r="T79" t="str">
+        <v/>
+      </c>
+      <c r="U79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -3760,6 +5638,30 @@
       <c r="M80" t="str">
         <v/>
       </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
+        <v/>
+      </c>
+      <c r="R80" t="str">
+        <v/>
+      </c>
+      <c r="S80" t="str">
+        <v/>
+      </c>
+      <c r="T80" t="str">
+        <v/>
+      </c>
+      <c r="U80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -3801,6 +5703,30 @@
       <c r="M81" t="str">
         <v/>
       </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
+        <v/>
+      </c>
+      <c r="R81" t="str">
+        <v/>
+      </c>
+      <c r="S81" t="str">
+        <v/>
+      </c>
+      <c r="T81" t="str">
+        <v/>
+      </c>
+      <c r="U81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -3842,6 +5768,30 @@
       <c r="M82" t="str">
         <v/>
       </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
+        <v/>
+      </c>
+      <c r="R82" t="str">
+        <v/>
+      </c>
+      <c r="S82" t="str">
+        <v/>
+      </c>
+      <c r="T82" t="str">
+        <v/>
+      </c>
+      <c r="U82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -3883,6 +5833,30 @@
       <c r="M83" t="str">
         <v/>
       </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
+        <v/>
+      </c>
+      <c r="R83" t="str">
+        <v/>
+      </c>
+      <c r="S83" t="str">
+        <v/>
+      </c>
+      <c r="T83" t="str">
+        <v/>
+      </c>
+      <c r="U83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -3924,6 +5898,30 @@
       <c r="M84" t="str">
         <v/>
       </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
+        <v/>
+      </c>
+      <c r="R84" t="str">
+        <v/>
+      </c>
+      <c r="S84" t="str">
+        <v/>
+      </c>
+      <c r="T84" t="str">
+        <v/>
+      </c>
+      <c r="U84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -3965,6 +5963,30 @@
       <c r="M85" t="str">
         <v/>
       </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
+        <v/>
+      </c>
+      <c r="R85" t="str">
+        <v/>
+      </c>
+      <c r="S85" t="str">
+        <v/>
+      </c>
+      <c r="T85" t="str">
+        <v/>
+      </c>
+      <c r="U85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4006,6 +6028,30 @@
       <c r="M86" t="str">
         <v/>
       </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
+        <v/>
+      </c>
+      <c r="R86" t="str">
+        <v/>
+      </c>
+      <c r="S86" t="str">
+        <v/>
+      </c>
+      <c r="T86" t="str">
+        <v/>
+      </c>
+      <c r="U86" t="str">
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
@@ -4047,6 +6093,30 @@
       <c r="M87" t="str">
         <v/>
       </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
+        <v/>
+      </c>
+      <c r="R87" t="str">
+        <v/>
+      </c>
+      <c r="S87" t="str">
+        <v/>
+      </c>
+      <c r="T87" t="str">
+        <v/>
+      </c>
+      <c r="U87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4088,6 +6158,30 @@
       <c r="M88" t="str">
         <v/>
       </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
+        <v/>
+      </c>
+      <c r="R88" t="str">
+        <v/>
+      </c>
+      <c r="S88" t="str">
+        <v/>
+      </c>
+      <c r="T88" t="str">
+        <v/>
+      </c>
+      <c r="U88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4129,6 +6223,30 @@
       <c r="M89" t="str">
         <v/>
       </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
+        <v/>
+      </c>
+      <c r="R89" t="str">
+        <v/>
+      </c>
+      <c r="S89" t="str">
+        <v/>
+      </c>
+      <c r="T89" t="str">
+        <v/>
+      </c>
+      <c r="U89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4170,6 +6288,30 @@
       <c r="M90" t="str">
         <v/>
       </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
+        <v/>
+      </c>
+      <c r="R90" t="str">
+        <v/>
+      </c>
+      <c r="S90" t="str">
+        <v/>
+      </c>
+      <c r="T90" t="str">
+        <v/>
+      </c>
+      <c r="U90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4211,6 +6353,30 @@
       <c r="M91" t="str">
         <v/>
       </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
+        <v/>
+      </c>
+      <c r="R91" t="str">
+        <v/>
+      </c>
+      <c r="S91" t="str">
+        <v/>
+      </c>
+      <c r="T91" t="str">
+        <v/>
+      </c>
+      <c r="U91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4252,6 +6418,30 @@
       <c r="M92" t="str">
         <v/>
       </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
+        <v/>
+      </c>
+      <c r="R92" t="str">
+        <v/>
+      </c>
+      <c r="S92" t="str">
+        <v/>
+      </c>
+      <c r="T92" t="str">
+        <v/>
+      </c>
+      <c r="U92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4293,6 +6483,30 @@
       <c r="M93" t="str">
         <v/>
       </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+      <c r="P93" t="str">
+        <v/>
+      </c>
+      <c r="Q93" t="str">
+        <v/>
+      </c>
+      <c r="R93" t="str">
+        <v/>
+      </c>
+      <c r="S93" t="str">
+        <v/>
+      </c>
+      <c r="T93" t="str">
+        <v/>
+      </c>
+      <c r="U93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4334,6 +6548,30 @@
       <c r="M94" t="str">
         <v/>
       </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+      <c r="P94" t="str">
+        <v/>
+      </c>
+      <c r="Q94" t="str">
+        <v/>
+      </c>
+      <c r="R94" t="str">
+        <v/>
+      </c>
+      <c r="S94" t="str">
+        <v/>
+      </c>
+      <c r="T94" t="str">
+        <v/>
+      </c>
+      <c r="U94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4375,6 +6613,30 @@
       <c r="M95" t="str">
         <v/>
       </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+      <c r="P95" t="str">
+        <v/>
+      </c>
+      <c r="Q95" t="str">
+        <v/>
+      </c>
+      <c r="R95" t="str">
+        <v/>
+      </c>
+      <c r="S95" t="str">
+        <v/>
+      </c>
+      <c r="T95" t="str">
+        <v/>
+      </c>
+      <c r="U95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -4416,6 +6678,30 @@
       <c r="M96" t="str">
         <v/>
       </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v/>
+      </c>
+      <c r="P96" t="str">
+        <v/>
+      </c>
+      <c r="Q96" t="str">
+        <v/>
+      </c>
+      <c r="R96" t="str">
+        <v/>
+      </c>
+      <c r="S96" t="str">
+        <v/>
+      </c>
+      <c r="T96" t="str">
+        <v/>
+      </c>
+      <c r="U96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -4457,6 +6743,30 @@
       <c r="M97" t="str">
         <v/>
       </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+      <c r="P97" t="str">
+        <v/>
+      </c>
+      <c r="Q97" t="str">
+        <v/>
+      </c>
+      <c r="R97" t="str">
+        <v/>
+      </c>
+      <c r="S97" t="str">
+        <v/>
+      </c>
+      <c r="T97" t="str">
+        <v/>
+      </c>
+      <c r="U97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -4498,6 +6808,30 @@
       <c r="M98" t="str">
         <v/>
       </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+      <c r="P98" t="str">
+        <v/>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98" t="str">
+        <v/>
+      </c>
+      <c r="S98" t="str">
+        <v/>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4539,6 +6873,30 @@
       <c r="M99" t="str">
         <v/>
       </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+      <c r="P99" t="str">
+        <v/>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99" t="str">
+        <v/>
+      </c>
+      <c r="S99" t="str">
+        <v/>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -4580,6 +6938,30 @@
       <c r="M100" t="str">
         <v/>
       </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+      <c r="P100" t="str">
+        <v/>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100" t="str">
+        <v/>
+      </c>
+      <c r="S100" t="str">
+        <v/>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -4621,6 +7003,30 @@
       <c r="M101" t="str">
         <v/>
       </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v/>
+      </c>
+      <c r="P101" t="str">
+        <v/>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101" t="str">
+        <v/>
+      </c>
+      <c r="S101" t="str">
+        <v/>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -4662,6 +7068,30 @@
       <c r="M102" t="str">
         <v/>
       </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v/>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102" t="str">
+        <v/>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -4703,6 +7133,30 @@
       <c r="M103" t="str">
         <v/>
       </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v/>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103" t="str">
+        <v/>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -4744,6 +7198,30 @@
       <c r="M104" t="str">
         <v/>
       </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v/>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104" t="str">
+        <v/>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -4785,6 +7263,30 @@
       <c r="M105" t="str">
         <v/>
       </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v/>
+      </c>
+      <c r="P105" t="str">
+        <v/>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105" t="str">
+        <v/>
+      </c>
+      <c r="S105" t="str">
+        <v/>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4826,6 +7328,30 @@
       <c r="M106" t="str">
         <v/>
       </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v/>
+      </c>
+      <c r="P106" t="str">
+        <v/>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106" t="str">
+        <v/>
+      </c>
+      <c r="S106" t="str">
+        <v/>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -4867,6 +7393,30 @@
       <c r="M107" t="str">
         <v/>
       </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v/>
+      </c>
+      <c r="P107" t="str">
+        <v/>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107" t="str">
+        <v/>
+      </c>
+      <c r="S107" t="str">
+        <v/>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -4908,6 +7458,30 @@
       <c r="M108" t="str">
         <v/>
       </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v/>
+      </c>
+      <c r="P108" t="str">
+        <v/>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108" t="str">
+        <v/>
+      </c>
+      <c r="S108" t="str">
+        <v/>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -4949,6 +7523,30 @@
       <c r="M109" t="str">
         <v/>
       </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v/>
+      </c>
+      <c r="P109" t="str">
+        <v/>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109" t="str">
+        <v/>
+      </c>
+      <c r="S109" t="str">
+        <v/>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -4990,6 +7588,30 @@
       <c r="M110" t="str">
         <v/>
       </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v/>
+      </c>
+      <c r="P110" t="str">
+        <v/>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110" t="str">
+        <v/>
+      </c>
+      <c r="S110" t="str">
+        <v/>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5031,6 +7653,30 @@
       <c r="M111" t="str">
         <v/>
       </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v/>
+      </c>
+      <c r="P111" t="str">
+        <v/>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111" t="str">
+        <v/>
+      </c>
+      <c r="S111" t="str">
+        <v/>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5072,6 +7718,30 @@
       <c r="M112" t="str">
         <v/>
       </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v/>
+      </c>
+      <c r="P112" t="str">
+        <v/>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112" t="str">
+        <v/>
+      </c>
+      <c r="S112" t="str">
+        <v/>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5113,6 +7783,30 @@
       <c r="M113" t="str">
         <v/>
       </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v/>
+      </c>
+      <c r="P113" t="str">
+        <v/>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113" t="str">
+        <v/>
+      </c>
+      <c r="S113" t="str">
+        <v/>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5154,6 +7848,30 @@
       <c r="M114" t="str">
         <v/>
       </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v/>
+      </c>
+      <c r="P114" t="str">
+        <v/>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114" t="str">
+        <v/>
+      </c>
+      <c r="S114" t="str">
+        <v/>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5195,6 +7913,30 @@
       <c r="M115" t="str">
         <v/>
       </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v/>
+      </c>
+      <c r="P115" t="str">
+        <v/>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115" t="str">
+        <v/>
+      </c>
+      <c r="S115" t="str">
+        <v/>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5236,6 +7978,30 @@
       <c r="M116" t="str">
         <v/>
       </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v/>
+      </c>
+      <c r="P116" t="str">
+        <v/>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116" t="str">
+        <v/>
+      </c>
+      <c r="S116" t="str">
+        <v/>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+      <c r="U116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5277,6 +8043,30 @@
       <c r="M117" t="str">
         <v/>
       </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v/>
+      </c>
+      <c r="P117" t="str">
+        <v/>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117" t="str">
+        <v/>
+      </c>
+      <c r="S117" t="str">
+        <v/>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5318,6 +8108,30 @@
       <c r="M118" t="str">
         <v/>
       </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v/>
+      </c>
+      <c r="P118" t="str">
+        <v/>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118" t="str">
+        <v/>
+      </c>
+      <c r="S118" t="str">
+        <v/>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5359,6 +8173,30 @@
       <c r="M119" t="str">
         <v/>
       </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v/>
+      </c>
+      <c r="P119" t="str">
+        <v/>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119" t="str">
+        <v/>
+      </c>
+      <c r="S119" t="str">
+        <v/>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5400,6 +8238,30 @@
       <c r="M120" t="str">
         <v/>
       </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v/>
+      </c>
+      <c r="P120" t="str">
+        <v/>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120" t="str">
+        <v/>
+      </c>
+      <c r="S120" t="str">
+        <v/>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5441,6 +8303,30 @@
       <c r="M121" t="str">
         <v/>
       </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v/>
+      </c>
+      <c r="P121" t="str">
+        <v/>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121" t="str">
+        <v/>
+      </c>
+      <c r="S121" t="str">
+        <v/>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5482,6 +8368,30 @@
       <c r="M122" t="str">
         <v/>
       </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v/>
+      </c>
+      <c r="P122" t="str">
+        <v/>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122" t="str">
+        <v/>
+      </c>
+      <c r="S122" t="str">
+        <v/>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5523,6 +8433,30 @@
       <c r="M123" t="str">
         <v/>
       </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v/>
+      </c>
+      <c r="P123" t="str">
+        <v/>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123" t="str">
+        <v/>
+      </c>
+      <c r="S123" t="str">
+        <v/>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5564,6 +8498,30 @@
       <c r="M124" t="str">
         <v/>
       </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v/>
+      </c>
+      <c r="P124" t="str">
+        <v/>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124" t="str">
+        <v/>
+      </c>
+      <c r="S124" t="str">
+        <v/>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5605,6 +8563,30 @@
       <c r="M125" t="str">
         <v/>
       </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v/>
+      </c>
+      <c r="P125" t="str">
+        <v/>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125" t="str">
+        <v/>
+      </c>
+      <c r="S125" t="str">
+        <v/>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5646,6 +8628,30 @@
       <c r="M126" t="str">
         <v/>
       </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126" t="str">
+        <v/>
+      </c>
+      <c r="S126" t="str">
+        <v/>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5687,6 +8693,30 @@
       <c r="M127" t="str">
         <v/>
       </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v/>
+      </c>
+      <c r="P127" t="str">
+        <v/>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127" t="str">
+        <v/>
+      </c>
+      <c r="S127" t="str">
+        <v/>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -5728,6 +8758,30 @@
       <c r="M128" t="str">
         <v/>
       </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v/>
+      </c>
+      <c r="P128" t="str">
+        <v/>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128" t="str">
+        <v/>
+      </c>
+      <c r="S128" t="str">
+        <v/>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -5769,6 +8823,30 @@
       <c r="M129" t="str">
         <v/>
       </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v/>
+      </c>
+      <c r="P129" t="str">
+        <v/>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129" t="str">
+        <v/>
+      </c>
+      <c r="S129" t="str">
+        <v/>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129" t="str">
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
@@ -5810,6 +8888,30 @@
       <c r="M130" t="str">
         <v/>
       </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v/>
+      </c>
+      <c r="P130" t="str">
+        <v/>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130" t="str">
+        <v/>
+      </c>
+      <c r="S130" t="str">
+        <v/>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -5851,6 +8953,30 @@
       <c r="M131" t="str">
         <v/>
       </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v/>
+      </c>
+      <c r="P131" t="str">
+        <v/>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131" t="str">
+        <v/>
+      </c>
+      <c r="S131" t="str">
+        <v/>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -5892,6 +9018,30 @@
       <c r="M132" t="str">
         <v/>
       </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v/>
+      </c>
+      <c r="P132" t="str">
+        <v/>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132" t="str">
+        <v/>
+      </c>
+      <c r="S132" t="str">
+        <v/>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -5933,6 +9083,30 @@
       <c r="M133" t="str">
         <v/>
       </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v/>
+      </c>
+      <c r="P133" t="str">
+        <v/>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133" t="str">
+        <v/>
+      </c>
+      <c r="S133" t="str">
+        <v/>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -5974,6 +9148,30 @@
       <c r="M134" t="str">
         <v/>
       </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v/>
+      </c>
+      <c r="P134" t="str">
+        <v/>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134" t="str">
+        <v/>
+      </c>
+      <c r="S134" t="str">
+        <v/>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6015,6 +9213,30 @@
       <c r="M135" t="str">
         <v/>
       </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v/>
+      </c>
+      <c r="P135" t="str">
+        <v/>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135" t="str">
+        <v/>
+      </c>
+      <c r="S135" t="str">
+        <v/>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6056,6 +9278,30 @@
       <c r="M136" t="str">
         <v/>
       </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v/>
+      </c>
+      <c r="P136" t="str">
+        <v/>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136" t="str">
+        <v/>
+      </c>
+      <c r="S136" t="str">
+        <v/>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6097,6 +9343,30 @@
       <c r="M137" t="str">
         <v/>
       </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v/>
+      </c>
+      <c r="P137" t="str">
+        <v/>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137" t="str">
+        <v/>
+      </c>
+      <c r="S137" t="str">
+        <v/>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6138,6 +9408,30 @@
       <c r="M138" t="str">
         <v/>
       </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v/>
+      </c>
+      <c r="P138" t="str">
+        <v/>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138" t="str">
+        <v/>
+      </c>
+      <c r="S138" t="str">
+        <v/>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6179,6 +9473,30 @@
       <c r="M139" t="str">
         <v/>
       </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
+        <v/>
+      </c>
+      <c r="P139" t="str">
+        <v/>
+      </c>
+      <c r="Q139" t="str">
+        <v/>
+      </c>
+      <c r="R139" t="str">
+        <v/>
+      </c>
+      <c r="S139" t="str">
+        <v/>
+      </c>
+      <c r="T139" t="str">
+        <v/>
+      </c>
+      <c r="U139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6220,6 +9538,30 @@
       <c r="M140" t="str">
         <v/>
       </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
+        <v/>
+      </c>
+      <c r="P140" t="str">
+        <v/>
+      </c>
+      <c r="Q140" t="str">
+        <v/>
+      </c>
+      <c r="R140" t="str">
+        <v/>
+      </c>
+      <c r="S140" t="str">
+        <v/>
+      </c>
+      <c r="T140" t="str">
+        <v/>
+      </c>
+      <c r="U140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -6261,6 +9603,30 @@
       <c r="M141" t="str">
         <v/>
       </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
+        <v/>
+      </c>
+      <c r="P141" t="str">
+        <v/>
+      </c>
+      <c r="Q141" t="str">
+        <v/>
+      </c>
+      <c r="R141" t="str">
+        <v/>
+      </c>
+      <c r="S141" t="str">
+        <v/>
+      </c>
+      <c r="T141" t="str">
+        <v/>
+      </c>
+      <c r="U141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -6302,6 +9668,30 @@
       <c r="M142" t="str">
         <v/>
       </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
+        <v/>
+      </c>
+      <c r="P142" t="str">
+        <v/>
+      </c>
+      <c r="Q142" t="str">
+        <v/>
+      </c>
+      <c r="R142" t="str">
+        <v/>
+      </c>
+      <c r="S142" t="str">
+        <v/>
+      </c>
+      <c r="T142" t="str">
+        <v/>
+      </c>
+      <c r="U142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -6343,6 +9733,30 @@
       <c r="M143" t="str">
         <v/>
       </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
+        <v/>
+      </c>
+      <c r="P143" t="str">
+        <v/>
+      </c>
+      <c r="Q143" t="str">
+        <v/>
+      </c>
+      <c r="R143" t="str">
+        <v/>
+      </c>
+      <c r="S143" t="str">
+        <v/>
+      </c>
+      <c r="T143" t="str">
+        <v/>
+      </c>
+      <c r="U143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -6384,6 +9798,30 @@
       <c r="M144" t="str">
         <v/>
       </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
+      <c r="R144" t="str">
+        <v/>
+      </c>
+      <c r="S144" t="str">
+        <v/>
+      </c>
+      <c r="T144" t="str">
+        <v/>
+      </c>
+      <c r="U144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -6425,6 +9863,30 @@
       <c r="M145" t="str">
         <v/>
       </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
+      <c r="R145" t="str">
+        <v/>
+      </c>
+      <c r="S145" t="str">
+        <v/>
+      </c>
+      <c r="T145" t="str">
+        <v/>
+      </c>
+      <c r="U145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -6466,6 +9928,30 @@
       <c r="M146" t="str">
         <v/>
       </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
+      <c r="R146" t="str">
+        <v/>
+      </c>
+      <c r="S146" t="str">
+        <v/>
+      </c>
+      <c r="T146" t="str">
+        <v/>
+      </c>
+      <c r="U146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6507,6 +9993,30 @@
       <c r="M147" t="str">
         <v/>
       </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
+      <c r="R147" t="str">
+        <v/>
+      </c>
+      <c r="S147" t="str">
+        <v/>
+      </c>
+      <c r="T147" t="str">
+        <v/>
+      </c>
+      <c r="U147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6548,6 +10058,30 @@
       <c r="M148" t="str">
         <v/>
       </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
+      <c r="R148" t="str">
+        <v/>
+      </c>
+      <c r="S148" t="str">
+        <v/>
+      </c>
+      <c r="T148" t="str">
+        <v/>
+      </c>
+      <c r="U148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6589,6 +10123,30 @@
       <c r="M149" t="str">
         <v/>
       </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
+      <c r="R149" t="str">
+        <v/>
+      </c>
+      <c r="S149" t="str">
+        <v/>
+      </c>
+      <c r="T149" t="str">
+        <v/>
+      </c>
+      <c r="U149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6630,6 +10188,30 @@
       <c r="M150" t="str">
         <v/>
       </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
+      <c r="R150" t="str">
+        <v/>
+      </c>
+      <c r="S150" t="str">
+        <v/>
+      </c>
+      <c r="T150" t="str">
+        <v/>
+      </c>
+      <c r="U150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6671,6 +10253,30 @@
       <c r="M151" t="str">
         <v/>
       </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
+      <c r="R151" t="str">
+        <v/>
+      </c>
+      <c r="S151" t="str">
+        <v/>
+      </c>
+      <c r="T151" t="str">
+        <v/>
+      </c>
+      <c r="U151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -6712,6 +10318,30 @@
       <c r="M152" t="str">
         <v/>
       </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
+      <c r="R152" t="str">
+        <v/>
+      </c>
+      <c r="S152" t="str">
+        <v/>
+      </c>
+      <c r="T152" t="str">
+        <v/>
+      </c>
+      <c r="U152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -6753,6 +10383,30 @@
       <c r="M153" t="str">
         <v/>
       </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
+      <c r="R153" t="str">
+        <v/>
+      </c>
+      <c r="S153" t="str">
+        <v/>
+      </c>
+      <c r="T153" t="str">
+        <v/>
+      </c>
+      <c r="U153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -6794,6 +10448,30 @@
       <c r="M154" t="str">
         <v/>
       </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
+      <c r="R154" t="str">
+        <v/>
+      </c>
+      <c r="S154" t="str">
+        <v/>
+      </c>
+      <c r="T154" t="str">
+        <v/>
+      </c>
+      <c r="U154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -6835,6 +10513,30 @@
       <c r="M155" t="str">
         <v/>
       </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
+      <c r="R155" t="str">
+        <v/>
+      </c>
+      <c r="S155" t="str">
+        <v/>
+      </c>
+      <c r="T155" t="str">
+        <v/>
+      </c>
+      <c r="U155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -6876,6 +10578,30 @@
       <c r="M156" t="str">
         <v/>
       </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
+      <c r="R156" t="str">
+        <v/>
+      </c>
+      <c r="S156" t="str">
+        <v/>
+      </c>
+      <c r="T156" t="str">
+        <v/>
+      </c>
+      <c r="U156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -6917,6 +10643,30 @@
       <c r="M157" t="str">
         <v/>
       </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
+      <c r="R157" t="str">
+        <v/>
+      </c>
+      <c r="S157" t="str">
+        <v/>
+      </c>
+      <c r="T157" t="str">
+        <v/>
+      </c>
+      <c r="U157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -6958,6 +10708,30 @@
       <c r="M158" t="str">
         <v/>
       </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
+      <c r="R158" t="str">
+        <v/>
+      </c>
+      <c r="S158" t="str">
+        <v/>
+      </c>
+      <c r="T158" t="str">
+        <v/>
+      </c>
+      <c r="U158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -6999,6 +10773,30 @@
       <c r="M159" t="str">
         <v/>
       </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
+      <c r="R159" t="str">
+        <v/>
+      </c>
+      <c r="S159" t="str">
+        <v/>
+      </c>
+      <c r="T159" t="str">
+        <v/>
+      </c>
+      <c r="U159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -7040,6 +10838,30 @@
       <c r="M160" t="str">
         <v/>
       </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
+      <c r="R160" t="str">
+        <v/>
+      </c>
+      <c r="S160" t="str">
+        <v/>
+      </c>
+      <c r="T160" t="str">
+        <v/>
+      </c>
+      <c r="U160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -7081,6 +10903,30 @@
       <c r="M161" t="str">
         <v/>
       </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
+      <c r="R161" t="str">
+        <v/>
+      </c>
+      <c r="S161" t="str">
+        <v/>
+      </c>
+      <c r="T161" t="str">
+        <v/>
+      </c>
+      <c r="U161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -7122,6 +10968,30 @@
       <c r="M162" t="str">
         <v/>
       </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
+      <c r="R162" t="str">
+        <v/>
+      </c>
+      <c r="S162" t="str">
+        <v/>
+      </c>
+      <c r="T162" t="str">
+        <v/>
+      </c>
+      <c r="U162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -7163,6 +11033,30 @@
       <c r="M163" t="str">
         <v/>
       </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
+      <c r="R163" t="str">
+        <v/>
+      </c>
+      <c r="S163" t="str">
+        <v/>
+      </c>
+      <c r="T163" t="str">
+        <v/>
+      </c>
+      <c r="U163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -7204,6 +11098,30 @@
       <c r="M164" t="str">
         <v/>
       </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
+      <c r="R164" t="str">
+        <v/>
+      </c>
+      <c r="S164" t="str">
+        <v/>
+      </c>
+      <c r="T164" t="str">
+        <v/>
+      </c>
+      <c r="U164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -7245,6 +11163,30 @@
       <c r="M165" t="str">
         <v/>
       </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
+      <c r="R165" t="str">
+        <v/>
+      </c>
+      <c r="S165" t="str">
+        <v/>
+      </c>
+      <c r="T165" t="str">
+        <v/>
+      </c>
+      <c r="U165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -7286,6 +11228,30 @@
       <c r="M166" t="str">
         <v/>
       </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
+      <c r="R166" t="str">
+        <v/>
+      </c>
+      <c r="S166" t="str">
+        <v/>
+      </c>
+      <c r="T166" t="str">
+        <v/>
+      </c>
+      <c r="U166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -7327,6 +11293,30 @@
       <c r="M167" t="str">
         <v/>
       </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
+      <c r="R167" t="str">
+        <v/>
+      </c>
+      <c r="S167" t="str">
+        <v/>
+      </c>
+      <c r="T167" t="str">
+        <v/>
+      </c>
+      <c r="U167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -7368,6 +11358,30 @@
       <c r="M168" t="str">
         <v/>
       </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
+      <c r="R168" t="str">
+        <v/>
+      </c>
+      <c r="S168" t="str">
+        <v/>
+      </c>
+      <c r="T168" t="str">
+        <v/>
+      </c>
+      <c r="U168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -7409,6 +11423,30 @@
       <c r="M169" t="str">
         <v/>
       </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
+      <c r="R169" t="str">
+        <v/>
+      </c>
+      <c r="S169" t="str">
+        <v/>
+      </c>
+      <c r="T169" t="str">
+        <v/>
+      </c>
+      <c r="U169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -7450,6 +11488,30 @@
       <c r="M170" t="str">
         <v/>
       </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
+      <c r="R170" t="str">
+        <v/>
+      </c>
+      <c r="S170" t="str">
+        <v/>
+      </c>
+      <c r="T170" t="str">
+        <v/>
+      </c>
+      <c r="U170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -7491,6 +11553,30 @@
       <c r="M171" t="str">
         <v/>
       </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
+      <c r="R171" t="str">
+        <v/>
+      </c>
+      <c r="S171" t="str">
+        <v/>
+      </c>
+      <c r="T171" t="str">
+        <v/>
+      </c>
+      <c r="U171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -7532,6 +11618,30 @@
       <c r="M172" t="str">
         <v/>
       </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
+      <c r="R172" t="str">
+        <v/>
+      </c>
+      <c r="S172" t="str">
+        <v/>
+      </c>
+      <c r="T172" t="str">
+        <v/>
+      </c>
+      <c r="U172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -7573,6 +11683,30 @@
       <c r="M173" t="str">
         <v/>
       </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
+      <c r="R173" t="str">
+        <v/>
+      </c>
+      <c r="S173" t="str">
+        <v/>
+      </c>
+      <c r="T173" t="str">
+        <v/>
+      </c>
+      <c r="U173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7614,6 +11748,30 @@
       <c r="M174" t="str">
         <v/>
       </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
+      <c r="R174" t="str">
+        <v/>
+      </c>
+      <c r="S174" t="str">
+        <v/>
+      </c>
+      <c r="T174" t="str">
+        <v/>
+      </c>
+      <c r="U174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7655,6 +11813,30 @@
       <c r="M175" t="str">
         <v/>
       </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
+      <c r="R175" t="str">
+        <v/>
+      </c>
+      <c r="S175" t="str">
+        <v/>
+      </c>
+      <c r="T175" t="str">
+        <v/>
+      </c>
+      <c r="U175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -7696,6 +11878,30 @@
       <c r="M176" t="str">
         <v/>
       </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
+      <c r="R176" t="str">
+        <v/>
+      </c>
+      <c r="S176" t="str">
+        <v/>
+      </c>
+      <c r="T176" t="str">
+        <v/>
+      </c>
+      <c r="U176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -7737,6 +11943,30 @@
       <c r="M177" t="str">
         <v/>
       </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
+      <c r="R177" t="str">
+        <v/>
+      </c>
+      <c r="S177" t="str">
+        <v/>
+      </c>
+      <c r="T177" t="str">
+        <v/>
+      </c>
+      <c r="U177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -7778,6 +12008,30 @@
       <c r="M178" t="str">
         <v/>
       </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
+      <c r="R178" t="str">
+        <v/>
+      </c>
+      <c r="S178" t="str">
+        <v/>
+      </c>
+      <c r="T178" t="str">
+        <v/>
+      </c>
+      <c r="U178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -7819,6 +12073,30 @@
       <c r="M179" t="str">
         <v/>
       </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
+      <c r="R179" t="str">
+        <v/>
+      </c>
+      <c r="S179" t="str">
+        <v/>
+      </c>
+      <c r="T179" t="str">
+        <v/>
+      </c>
+      <c r="U179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -7860,6 +12138,30 @@
       <c r="M180" t="str">
         <v/>
       </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
+      <c r="R180" t="str">
+        <v/>
+      </c>
+      <c r="S180" t="str">
+        <v/>
+      </c>
+      <c r="T180" t="str">
+        <v/>
+      </c>
+      <c r="U180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -7901,6 +12203,30 @@
       <c r="M181" t="str">
         <v/>
       </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
+      <c r="R181" t="str">
+        <v/>
+      </c>
+      <c r="S181" t="str">
+        <v/>
+      </c>
+      <c r="T181" t="str">
+        <v/>
+      </c>
+      <c r="U181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -7942,6 +12268,30 @@
       <c r="M182" t="str">
         <v/>
       </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
+      <c r="R182" t="str">
+        <v/>
+      </c>
+      <c r="S182" t="str">
+        <v/>
+      </c>
+      <c r="T182" t="str">
+        <v/>
+      </c>
+      <c r="U182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -7983,6 +12333,30 @@
       <c r="M183" t="str">
         <v/>
       </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
+      <c r="R183" t="str">
+        <v/>
+      </c>
+      <c r="S183" t="str">
+        <v/>
+      </c>
+      <c r="T183" t="str">
+        <v/>
+      </c>
+      <c r="U183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -8024,6 +12398,30 @@
       <c r="M184" t="str">
         <v/>
       </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
+      <c r="R184" t="str">
+        <v/>
+      </c>
+      <c r="S184" t="str">
+        <v/>
+      </c>
+      <c r="T184" t="str">
+        <v/>
+      </c>
+      <c r="U184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -8065,6 +12463,30 @@
       <c r="M185" t="str">
         <v/>
       </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
+      <c r="R185" t="str">
+        <v/>
+      </c>
+      <c r="S185" t="str">
+        <v/>
+      </c>
+      <c r="T185" t="str">
+        <v/>
+      </c>
+      <c r="U185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -8106,6 +12528,30 @@
       <c r="M186" t="str">
         <v/>
       </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
+      <c r="R186" t="str">
+        <v/>
+      </c>
+      <c r="S186" t="str">
+        <v/>
+      </c>
+      <c r="T186" t="str">
+        <v/>
+      </c>
+      <c r="U186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -8147,6 +12593,30 @@
       <c r="M187" t="str">
         <v/>
       </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
+      <c r="R187" t="str">
+        <v/>
+      </c>
+      <c r="S187" t="str">
+        <v/>
+      </c>
+      <c r="T187" t="str">
+        <v/>
+      </c>
+      <c r="U187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -8188,6 +12658,30 @@
       <c r="M188" t="str">
         <v/>
       </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
+      <c r="R188" t="str">
+        <v/>
+      </c>
+      <c r="S188" t="str">
+        <v/>
+      </c>
+      <c r="T188" t="str">
+        <v/>
+      </c>
+      <c r="U188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -8229,6 +12723,30 @@
       <c r="M189" t="str">
         <v/>
       </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
+      <c r="R189" t="str">
+        <v/>
+      </c>
+      <c r="S189" t="str">
+        <v/>
+      </c>
+      <c r="T189" t="str">
+        <v/>
+      </c>
+      <c r="U189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -8270,6 +12788,30 @@
       <c r="M190" t="str">
         <v/>
       </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
+      <c r="R190" t="str">
+        <v/>
+      </c>
+      <c r="S190" t="str">
+        <v/>
+      </c>
+      <c r="T190" t="str">
+        <v/>
+      </c>
+      <c r="U190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -8311,6 +12853,30 @@
       <c r="M191" t="str">
         <v/>
       </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
+      <c r="R191" t="str">
+        <v/>
+      </c>
+      <c r="S191" t="str">
+        <v/>
+      </c>
+      <c r="T191" t="str">
+        <v/>
+      </c>
+      <c r="U191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -8352,6 +12918,30 @@
       <c r="M192" t="str">
         <v/>
       </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
+      <c r="R192" t="str">
+        <v/>
+      </c>
+      <c r="S192" t="str">
+        <v/>
+      </c>
+      <c r="T192" t="str">
+        <v/>
+      </c>
+      <c r="U192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -8393,6 +12983,30 @@
       <c r="M193" t="str">
         <v/>
       </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
+      <c r="R193" t="str">
+        <v/>
+      </c>
+      <c r="S193" t="str">
+        <v/>
+      </c>
+      <c r="T193" t="str">
+        <v/>
+      </c>
+      <c r="U193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -8434,6 +13048,30 @@
       <c r="M194" t="str">
         <v/>
       </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
+      <c r="R194" t="str">
+        <v/>
+      </c>
+      <c r="S194" t="str">
+        <v/>
+      </c>
+      <c r="T194" t="str">
+        <v/>
+      </c>
+      <c r="U194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -8475,6 +13113,30 @@
       <c r="M195" t="str">
         <v/>
       </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
+      <c r="R195" t="str">
+        <v/>
+      </c>
+      <c r="S195" t="str">
+        <v/>
+      </c>
+      <c r="T195" t="str">
+        <v/>
+      </c>
+      <c r="U195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -8516,6 +13178,30 @@
       <c r="M196" t="str">
         <v/>
       </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
+      <c r="R196" t="str">
+        <v/>
+      </c>
+      <c r="S196" t="str">
+        <v/>
+      </c>
+      <c r="T196" t="str">
+        <v/>
+      </c>
+      <c r="U196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -8557,6 +13243,30 @@
       <c r="M197" t="str">
         <v/>
       </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
+      <c r="R197" t="str">
+        <v/>
+      </c>
+      <c r="S197" t="str">
+        <v/>
+      </c>
+      <c r="T197" t="str">
+        <v/>
+      </c>
+      <c r="U197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -8598,6 +13308,30 @@
       <c r="M198" t="str">
         <v/>
       </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
+      <c r="R198" t="str">
+        <v/>
+      </c>
+      <c r="S198" t="str">
+        <v/>
+      </c>
+      <c r="T198" t="str">
+        <v/>
+      </c>
+      <c r="U198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -8639,6 +13373,30 @@
       <c r="M199" t="str">
         <v/>
       </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
+      <c r="R199" t="str">
+        <v/>
+      </c>
+      <c r="S199" t="str">
+        <v/>
+      </c>
+      <c r="T199" t="str">
+        <v/>
+      </c>
+      <c r="U199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8680,6 +13438,30 @@
       <c r="M200" t="str">
         <v/>
       </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
+      <c r="R200" t="str">
+        <v/>
+      </c>
+      <c r="S200" t="str">
+        <v/>
+      </c>
+      <c r="T200" t="str">
+        <v/>
+      </c>
+      <c r="U200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -8721,40 +13503,169 @@
       <c r="M201" t="str">
         <v/>
       </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
+      <c r="R201" t="str">
+        <v/>
+      </c>
+      <c r="S201" t="str">
+        <v/>
+      </c>
+      <c r="T201" t="str">
+        <v/>
+      </c>
+      <c r="U201" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U201"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
-  <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="21.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="27.83203125" customWidth="1"/>
-    <col min="10" max="10" width="39.83203125" customWidth="1"/>
-    <col min="11" max="11" width="40.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:U4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Exemplo de preenchimento</v>
       </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+      <c r="E1" t="str">
+        <v/>
+      </c>
+      <c r="F1" t="str">
+        <v/>
+      </c>
+      <c r="G1" t="str">
+        <v/>
+      </c>
+      <c r="H1" t="str">
+        <v/>
+      </c>
+      <c r="I1" t="str">
+        <v/>
+      </c>
+      <c r="J1" t="str">
+        <v/>
+      </c>
+      <c r="K1" t="str">
+        <v/>
+      </c>
+      <c r="L1" t="str">
+        <v/>
+      </c>
+      <c r="M1" t="str">
+        <v/>
+      </c>
+      <c r="N1" t="str">
+        <v/>
+      </c>
+      <c r="O1" t="str">
+        <v/>
+      </c>
+      <c r="P1" t="str">
+        <v/>
+      </c>
+      <c r="Q1" t="str">
+        <v/>
+      </c>
+      <c r="R1" t="str">
+        <v/>
+      </c>
+      <c r="S1" t="str">
+        <v/>
+      </c>
+      <c r="T1" t="str">
+        <v/>
+      </c>
+      <c r="U1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
         <v/>
       </c>
     </row>
@@ -8772,30 +13683,54 @@
         <v>cnpj</v>
       </c>
       <c r="E3" t="str">
+        <v>endereco_logradouro</v>
+      </c>
+      <c r="F3" t="str">
+        <v>endereco_numero</v>
+      </c>
+      <c r="G3" t="str">
+        <v>endereco_complemento</v>
+      </c>
+      <c r="H3" t="str">
+        <v>endereco_bairro</v>
+      </c>
+      <c r="I3" t="str">
+        <v>endereco_cidade</v>
+      </c>
+      <c r="J3" t="str">
+        <v>endereco_uf</v>
+      </c>
+      <c r="K3" t="str">
+        <v>endereco_cep</v>
+      </c>
+      <c r="L3" t="str">
         <v>administradora</v>
       </c>
-      <c r="F3" t="str">
+      <c r="M3" t="str">
         <v>vencimento_cota_dia</v>
       </c>
-      <c r="G3" t="str">
+      <c r="N3" t="str">
         <v>valor_cota_condominial</v>
       </c>
-      <c r="H3" t="str">
+      <c r="O3" t="str">
         <v>inicio_cobranca_dias</v>
       </c>
-      <c r="I3" t="str">
+      <c r="P3" t="str">
+        <v>dias_expiracao_regua_pre_juridico</v>
+      </c>
+      <c r="Q3" t="str">
         <v>classificacao_operacional</v>
       </c>
-      <c r="J3" t="str">
+      <c r="R3" t="str">
         <v>parcelas_acordo_sem_aprovacao_sindico</v>
       </c>
-      <c r="K3" t="str">
+      <c r="S3" t="str">
         <v>dias_reemissao_parcela_acordo_atrasada</v>
       </c>
-      <c r="L3" t="str">
+      <c r="T3" t="str">
         <v>status</v>
       </c>
-      <c r="M3" t="str">
+      <c r="U3" t="str">
         <v>observacoes</v>
       </c>
     </row>
@@ -8813,36 +13748,60 @@
         <v>12.345.678/0001-90</v>
       </c>
       <c r="E4" t="str">
+        <v>Rua Exemplo</v>
+      </c>
+      <c r="F4" t="str">
+        <v>100</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Bloco A</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Centro</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Sao Paulo</v>
+      </c>
+      <c r="J4" t="str">
+        <v>SP</v>
+      </c>
+      <c r="K4" t="str">
+        <v>01000-000</v>
+      </c>
+      <c r="L4" t="str">
         <v>Administradora Exemplo</v>
       </c>
-      <c r="F4">
+      <c r="M4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="N4">
         <v>1250.5</v>
       </c>
-      <c r="H4">
+      <c r="O4">
         <v>30</v>
       </c>
-      <c r="I4" t="str">
+      <c r="P4">
+        <v>60</v>
+      </c>
+      <c r="Q4" t="str">
         <v>prata</v>
       </c>
-      <c r="J4">
+      <c r="R4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="S4">
         <v>0</v>
       </c>
-      <c r="L4" t="str">
+      <c r="T4" t="str">
         <v>ativo</v>
       </c>
-      <c r="M4" t="str">
+      <c r="U4" t="str">
         <v>Linha exemplo; substitua pelos dados reais</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U4"/>
   </ignoredErrors>
 </worksheet>
 </file>